--- a/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
+++ b/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
@@ -989,7 +989,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stream_core monitor gating + block_ready (projects/components/dmas/stream/rtl/macro/stream_core.sv, rtl/amba/monitor/axi4_master_rd_mon.sv, rtl/amba/monitor/axi4_master_wr_mon.sv, rtl/amba/monitor/axi_monitor_base.sv)</t>
+          <t>stream_core monitor gating + block_ready (projects/components/dmas/stream/rtl/macro/stream_core.sv, rtl/amba/axi4/axi4_master_rd_mon.sv, rtl/amba/axi4/axi4_master_wr_mon.sv, rtl/amba/monitor/axi_monitor_base.sv)</t>
         </is>
       </c>
     </row>
@@ -1008,14 +1008,14 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/monitor/axi4_master_rd_mon.sv:477-478</t>
+          <t>rtl/amba/axi4/axi4_master_rd_mon.sv:479-480</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>fub_axi_arready = w_core_fub_axi_arready &amp; (w_block_ready | ~cfg_monitor_enable)   [identical shape for AW: rtl/amba/monitor/axi4_master_wr_mon.sv:482-483]</t>
+          <t>fub_axi_arready = w_core_fub_axi_arready &amp; (w_block_ready | ~cfg_monitor_enable)   [identical shape for AW: rtl/amba/axi4/axi4_master_wr_mon.sv:482-483]</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:471</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:484</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:454-456, :797-802</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:467-469, :810-815</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1102-1110, :1147-1153. Size cycles to the workload: an undersized 1000-cycle default falsely timed out 8-channel contention (top multi_channel hang, fixed by programming the timeout via APB).</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1115-1123, :1160-1166. Size cycles to the workload: an undersized 1000-cycle default falsely timed out 8-channel contention (top multi_channel hang, fixed by programming the timeout via APB).</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:911-927</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:924-940</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:660/:715; rtl/amba/monitor/axi4_master_rd_mon.sv:477-478</t>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:699/:754; rtl/amba/axi4/axi4_master_rd_mon.sv:479-480</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1186-1317 (emitter). Standard integration: gaxi FIFO or monbus_group SRAM behind the port.</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1199-1330 (emitter). Standard integration: gaxi FIFO or monbus_group SRAM behind the port.</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1234-1248</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1247-1261</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1209</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1222</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1296-1309</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1309-1322</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:962-965</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:975-978</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:988-992</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1001-1005</t>
         </is>
       </c>
     </row>
@@ -4645,40 +4645,45 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>w_transfer_complete  (per-descriptor advance gate)</t>
+          <t>w_addrgen_start  (run-base generator start; EXT only)</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:893</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:317</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>w_transfer_complete = w_read_complete &amp;&amp; w_write_issued   [ISSUE-based on purpose: chained descriptors stream while their writes commit in the background]</t>
+          <t>w_addrgen_start = w_state_fetch_desc &amp;&amp; !r_fetch_desc_d &amp;&amp; w_is_ext</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = read_complete/write_issued   cols = </t>
+          <t>rows = state_fetch_desc/entry_edge   cols = is_ext</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1). Commit-gating this (as a past edit did) serializes the write drain at every descriptor boundary - the regression that motivated the issue/commit split.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). The is_ext term is the TASK-059 FIX: without it a LEGACY descriptor also pulses start, running stream_run_addr_gen with its own base and STALE r_descriptor_ext strides. The generator's run-base FIFO has no flush (gaxi_fifo_sync clears only on rst_n) and legacy never consumes bases, so those bogus bases are consumed by the NEXT chained strided/transpose descriptor -&gt; reads the wrong source and writes into the previous descriptor's region (silent corruption). A contiguous EXT descriptor hides it (single-run generation emits zero bases). See known_issues/resolved/extended_chained_transpose.md.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4691,6 +4696,9 @@
       <c r="B43" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="C43" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -4701,6 +4709,9 @@
       <c r="B44" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="C44" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -4708,7 +4719,10 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4721,49 +4735,47 @@
       <c r="B46" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="C46" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>CH_XFER_DATA exit decision</t>
+          <t>w_transfer_complete  (per-descriptor advance gate)</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:510-514</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:906</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>if (w_wr_advance) stay-XFER (in-place descriptor advance) ; else if (w_transfer_complete &amp;&amp; !r_rd_ahead) -&gt; CH_COMPLETE ; else hold</t>
+          <t>w_transfer_complete = w_read_complete &amp;&amp; w_write_issued   [ISSUE-based on purpose: chained descriptors stream while their writes commit in the background]</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rows = wr_advance/transfer_complete   cols = rd_ahead</t>
+          <t xml:space="preserve">rows = read_complete/write_issued   cols = </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: advance fills the whole wr_advance=1 half (priority). COMPLETE only at (0,1,0): while read runs ahead (rd_ahead=1) the completion exit is SUPPRESSED because w_transfer_complete keys off the READ counter which already refers to descriptor N+1.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1). Commit-gating this (as a past edit did) serializes the write drain at every descriptor boundary - the regression that motivated the issue/commit split.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4773,15 +4785,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
+      <c r="B55" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4790,15 +4795,8 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
+      <c r="B56" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4807,15 +4805,8 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
+      <c r="B57" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -4824,54 +4815,52 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
+      <c r="B58" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>CH_COMPLETE exit decision</t>
+          <t>CH_XFER_DATA exit decision</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:527-531</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:523-527</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>if (next_ptr != 0 &amp;&amp; !last) -&gt; CH_NEXT_DESC (advance NOW, issue-based) ; else if (w_write_complete) -&gt; CH_IDLE ; else hold</t>
+          <t>if (w_wr_advance) stay-XFER (in-place descriptor advance) ; else if (w_transfer_complete &amp;&amp; !r_rd_ahead) -&gt; CH_COMPLETE ; else hold</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = chained/write_complete   cols = </t>
+          <t>rows = wr_advance/transfer_complete   cols = rd_ahead</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: chained=1 half advances immediately regardless of commits (streaming). IDLE only at (0,1): the LAST descriptor holds here until every write has COMMITTED - the channel is never reported done while data still drains.</t>
+          <t>CHECK BY INSPECTION: advance fills the whole wr_advance=1 half (priority). COMPLETE only at (0,1,0): while read runs ahead (rd_ahead=1) the completion exit is SUPPRESSED because w_transfer_complete keys off the READ counter which already refers to descriptor N+1.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4886,6 +4875,11 @@
           <t>hold</t>
         </is>
       </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -4893,9 +4887,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>IDLE</t>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>hold</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4906,12 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>NEXT_DESC</t>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>advance</t>
         </is>
       </c>
     </row>
@@ -4919,286 +4923,207 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>NEXT_DESC</t>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>advance</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>w_rd_peek  (read-ahead loads next descriptor)</t>
+          <t>CH_COMPLETE exit decision</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:916-918</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:540-544</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>w_rd_peek = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; !r_rd_ahead &amp;&amp; (r_read_beats_remaining==0) &amp;&amp; !w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid   [head_ok = w_desc_chained &amp;&amp; descriptor_valid]</t>
+          <t>if (next_ptr != 0 &amp;&amp; !last) -&gt; CH_NEXT_DESC (advance NOW, issue-based) ; else if (w_write_complete) -&gt; CH_IDLE ; else hold</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rows = prefetch_en/state_xfer   cols = rd_ahead/rd_done   pages = write_issued/head_ok</t>
+          <t xml:space="preserve">rows = chained/write_complete   cols = </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the [write_issued=0, head_ok=1] page, single cell (prefetch_en=1, state_xfer=1, rd_ahead=0, rd_done=1). rd_ahead=0 caps read-ahead at ONE descriptor; write_issued=0 means the write side still owns the FIFO head, so peek must NOT pop it.</t>
+          <t>CHECK BY INSPECTION: chained=1 half advances immediately regardless of commits (streaming). IDLE only at (0,1): the LAST descriptor holds here until every write has COMMITTED - the channel is never reported done while data still drains.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>[write_issued=0, head_ok=0]</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="8" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>hold</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>0</v>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>0</v>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>NEXT_DESC</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>NEXT_DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>w_rd_peek  (read-ahead loads next descriptor)</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:929-931</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>w_rd_peek = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; !r_rd_ahead &amp;&amp; (r_read_beats_remaining==0) &amp;&amp; !w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid   [head_ok = w_desc_chained &amp;&amp; descriptor_valid]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>rows = prefetch_en/state_xfer   cols = rd_ahead/rd_done   pages = write_issued/head_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the [write_issued=0, head_ok=1] page, single cell (prefetch_en=1, state_xfer=1, rd_ahead=0, rd_done=1). rd_ahead=0 caps read-ahead at ONE descriptor; write_issued=0 means the write side still owns the FIFO head, so peek must NOT pop it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>[write_issued=0, head_ok=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>[write_issued=0, head_ok=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="8" t="inlineStr">
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="B92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>[write_issued=1, head_ok=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B94" s="9" t="n">
@@ -5217,100 +5142,100 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>[write_issued=0, head_ok=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>[write_issued=1, head_ok=1]</t>
-        </is>
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C101" s="9" t="n">
-        <v>0</v>
+      <c r="C101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="D101" s="9" t="n">
         <v>0</v>
@@ -5322,126 +5247,179 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>[write_issued=1, head_ok=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="9" t="n">
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>w_wr_advance  (in-place descriptor advance + FIFO pop)</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:926-927</t>
-        </is>
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>w_wr_advance = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid</t>
-        </is>
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>rows = prefetch_en/state_xfer   cols = write_issued/chained   pages = desc_valid</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the [desc_valid=1] page, single cell at all-ones. This is the ONLY XFER-state descriptor_ready source: it pops the FIFO head that peek borrowed. prefetch_en=0 forces the whole map to 0 (lockstep A/B on one bitstream).</t>
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>[write_issued=1, head_ok=1]</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>[desc_valid=0]</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="8" t="inlineStr">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B114" s="9" t="n">
@@ -5460,7 +5438,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B115" s="9" t="n">
@@ -5479,188 +5457,186 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>w_wr_advance  (in-place descriptor advance + FIFO pop)</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:939-940</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>w_wr_advance = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>rows = prefetch_en/state_xfer   cols = write_issued/chained   pages = desc_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the [desc_valid=1] page, single cell at all-ones. This is the ONLY XFER-state descriptor_ready source: it pops the FIFO head that peek borrowed. prefetch_en=0 forces the whole map to 0 (lockstep A/B on one bitstream).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>[desc_valid=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t>[desc_valid=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="inlineStr">
-        <is>
-          <t>descriptor_ready  (FIFO pop)</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1064-1066</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>descriptor_ready = (state==CH_IDLE) || (state==CH_NEXT_DESC) || w_wr_advance</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>rows = state_idle/state_next_desc   cols = wr_advance</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: OR of three sources; zero only at all-zeros. idle/next_desc are mutually exclusive (one-hot FSM) and wr_advance can only be 1 in CH_XFER_DATA, so at most one source is live per cycle - the (1,1,x) cells are unreachable cover.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>00</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -5673,8 +5649,14 @@
       <c r="B133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C133" s="10" t="n">
-        <v>1</v>
+      <c r="C133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5683,11 +5665,17 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="n">
-        <v>1</v>
+      <c r="B134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -5696,11 +5684,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B135" s="10" t="n">
+      <c r="B135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C135" s="10" t="n">
-        <v>1</v>
+      <c r="E135" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5709,43 +5703,49 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="10" t="n">
-        <v>1</v>
+      <c r="B136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>w_hard_error  (fatal -&gt; sticky CH_ERROR)</t>
+          <t>descriptor_ready  (FIFO pop)</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1157-1158</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1077-1079</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky   [rd_any = live|sticky, wr_any = live|sticky]</t>
+          <t>descriptor_ready = (state==CH_IDLE) || (state==CH_NEXT_DESC) || w_wr_advance</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rows = descriptor_error/rd_any   cols = wr_any</t>
+          <t>rows = state_idle/state_next_desc   cols = wr_advance</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at all-zeros (pure OR). A bare timeout window is deliberately NOT in this cone - it escalates separately via w_timeout_escalate (strikes &gt;= cfg_sched_timeout_limit).</t>
+          <t>CHECK BY INSPECTION: OR of three sources; zero only at all-zeros. idle/next_desc are mutually exclusive (one-hot FSM) and wr_advance can only be 1 in CH_XFER_DATA, so at most one source is live per cycle - the (1,1,x) cells are unreachable cover.</t>
         </is>
       </c>
     </row>
@@ -5816,183 +5816,280 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
+          <t>w_hard_error  (fatal -&gt; sticky CH_ERROR)</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1170-1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky   [rd_any = live|sticky, wr_any = live|sticky]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>rows = descriptor_error/rd_any   cols = wr_any</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at all-zeros (pure OR). A bare timeout window is deliberately NOT in this cone - it escalates separately via w_timeout_escalate (strikes &gt;= cfg_sched_timeout_limit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
           <t>r_timeout_counter next-value (priority order)</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1102-1110</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1115-1123</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>w_timeout_expired = cfg_sched_timeout_enable &amp;&amp; (counter &gt;= cfg_sched_timeout_cycles) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1147-1148). Escalation: w_timeout_escalate = (limit != 0) &amp;&amp; (strikes &gt;= limit) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1152-1153); strikes clear on any progress or CH_IDLE.</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>condition (first match wins)</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t>sched_wr_done_strobe || sched_wr_commit_strobe</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>ANY write progress (AW issue OR B commit) re-arms - commits count as progress because completion is commit-gated</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>w_timeout_expired</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>window elapsed -&gt; re-arm and keep waiting (SOFT timeout, one pulse per window)</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>sched_wr_valid &amp;&amp; !sched_wr_ready</t>
         </is>
       </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>counter + 1</t>
         </is>
       </c>
-      <c r="C156" s="4" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>genuinely waiting on the write engine</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>otherwise</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>not waiting</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
         <is>
           <t>FSM transition priority</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:451-465</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:464-478</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>CH_ERROR self-loops until channel reset; scheduler_idle reports CH_IDLE only (a wedged channel must NOT read idle).</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="4" t="n">
+    <row r="175">
+      <c r="A175" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>r_channel_reset_active</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr">
         <is>
           <t>-&gt; CH_IDLE (overrides all)</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="4" t="n">
+    <row r="176">
+      <c r="A176" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t>w_hard_error || w_timeout_escalate</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr">
         <is>
           <t>-&gt; CH_ERROR (sticky)</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="4" t="n">
+    <row r="177">
+      <c r="A177" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>state case (normal transitions)</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr">
         <is>
           <t>see exit-decision maps</t>
         </is>

--- a/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
+++ b/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,14 @@
     </font>
     <font>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C6500"/>
     </font>
   </fonts>
   <fills count="4">
@@ -85,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,6 +110,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -111,7 +120,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -973,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1020,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/axi4/axi4_master_rd_mon.sv:479-480</t>
+          <t>rtl/amba/axi4/axi4_master_rd_mon.sv:496-480</t>
         </is>
       </c>
     </row>
@@ -1033,351 +1045,407 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>w_block_ready  (monitor capacity)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>rtl/amba/monitor/axi_monitor_base.sv:483-485</t>
-        </is>
+      <c r="C15" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: core_ready &amp; !mon_enable  |  core_ready &amp; block_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>w_block_ready  (monitor capacity)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_base.sv:483-485</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>block_ready = (MAX_TRANSACTIONS &gt; BLOCK_MARGIN) ? (active_count &lt; MAX_TRANSACTIONS - BLOCK_MARGIN) : 1'b1   [vars: max_gt_margin (param, compile-time), count_below (comparator)]</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = max_gt_margin/count_below   cols = </t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: block_ready follows count_below whenever the table is big enough to carry a margin; degenerate tables never block. POLARITY is the loaded gun here: 1 = proceed. The inverted pre-fix polarity deadlocked every upstream handshake at reset.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B28" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B31" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !max_gt_margin  |  count_below</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>saturation-recovery contract (stream default sizing)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>rtl/amba/monitor/axi_monitor_base.sv:456-485, rtl/amba/includes/monitor_common_pkg.sv:114-116, projects/components/dmas/stream/rtl/macro/stream_core.sv:73-74</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>The reopen threshold sits STRICTLY ABOVE the command cap (67 &gt; 66): even a table whose command entries are all permanently in flight recovers block_ready as soon as orphan entries drain. The old flat MAX-3 margin parked the table exactly AT the threshold and never re-asserted (stream_core multi-channel wedge). Undersizing MAX_TRANSACTIONS on purpose (mon_small config) therefore throttles-and-recovers, never deadlocks.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>expression</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>8ch default value</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>MAX_TRANSACTIONS</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>NUM_CHANNELS * AR_MAX_OUTSTANDING + 4</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>cmd_entry_reserve(MAX)</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>(MAX &gt;= 16) ? 2 : 0</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>command-entry cap (trans_mgr)</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>MAX - reserve</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>BLOCK_MARGIN</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>reserve - 1 (or flat 3 if reserve==0)</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>block threshold</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>block when active_count &gt;= MAX - margin</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>&gt;= 67</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>reopen threshold</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>re-assert when active_count &lt; MAX - margin</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>&lt; 67</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>monitor enable tie-off (build-level gate)</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:641-732</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>e.g. projects/components/dmas/stream/rtl/macro/stream_core.sv:660 (enabled branch) vs :715 (tied-off branch). The always-on axi_bus_meter perf buckets survive USE_AXI_MONITORS=0 by design - only the heavy monitors and histograms are gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>USE_AXI_MONITORS</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>int_cfg_*_mon_enable</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>effect</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>BLOCK_MARGIN</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>reserve - 1 (or flat 3 if reserve==0)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B42" s="4">
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>block threshold</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>block when active_count &gt;= MAX - margin</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>&gt;= 67</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>reopen threshold</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>re-assert when active_count &lt; MAX - margin</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 67</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>monitor enable tie-off (build-level gate)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:641-732</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>e.g. projects/components/dmas/stream/rtl/macro/stream_core.sv:660 (enabled branch) vs :715 (tied-off branch). The always-on axi_bus_meter perf buckets survive USE_AXI_MONITORS=0 by design - only the heavy monitors and histograms are gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>USE_AXI_MONITORS</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>int_cfg_*_mon_enable</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B50" s="4">
         <f> cfg_*_mon_enable (CSR)</f>
         <v/>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>runtime on/off; wrapper instantiates the monitor (USE_MONITOR=1)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B43" s="4">
+      <c r="B51" s="4">
         <f> 1'b0 (tied)</f>
         <v/>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>monitor logic absent, w_block_ready tied 1: bare skid, zero datapath interference</t>
         </is>
@@ -2127,7 +2195,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:484</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:501</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2489,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:699/:754; rtl/amba/axi4/axi4_master_rd_mon.sv:479-480</t>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:779/:840; rtl/amba/axi4/axi4_master_rd_mon.sv:496-480</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2809,7 +2877,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>w_arb_request[i] = sched_rd_valid[i] &amp;&amp; w_space_ok[i] &amp;&amp; w_below_outstanding_limit[i]   [below_limit = !r_outstanding_limit]</t>
+          <t>w_arb_request[i] = sched_rd_valid[i] &amp;&amp; w_space_ok[i] &amp;&amp; w_below_outstanding_limit[i]</t>
         </is>
       </c>
     </row>
@@ -2827,593 +2895,794 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>sched_rd_valid</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>sched_rd_valid[i]  -- scheduler's per-channel read request (input port)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:327</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>space_ok</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>w_space_ok[i] = axi_rd_alloc_space_free[i] &gt;= w_transfer_size[i]+1</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:316</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>below_limit</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>w_below_outstanding_limit[i] = !r_outstanding_limit[i]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:321</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three and nothing else. The per-channel index i is a generate replication, not a variable of the decision. Everything else the read engine knows (burst size, addresses, IDs) affects WHAT is issued, never WHETHER: w_transfer_size feeds space_ok and is already folded into that axis, and the arbiter's own state is downstream of this signal, not upstream. No don't-cares: all 8 combinations are reachable, since the three axes come from three independent sources (scheduler, SRAM allocator, outstanding counter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="10" t="n">
+      <c r="B19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="B20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: sched_rd_valid &amp; space_ok &amp; below_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      sched_rd_valid &amp; space_ok &amp; below_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>w_space_ok / w_transfer_size sub-terms</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:312-316</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>space_free is registered twice on its way out of the SRAM controller; the read side tolerates the staleness because alloc reservations only shrink it (safe direction).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>RTL (mirror of)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>w_transfer_size[i]</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>(sched_rd_beats &lt;= cfg+1) ? sched_rd_beats-1 : cfg</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>AxLEN value: full configured burst, or the shorter final burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>w_space_ok[i]</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>axi_rd_alloc_space_free[i] &gt;= w_transfer_size[i]+1</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>SRAM channel can hold the whole burst BEFORE the AR issues (pre-allocation; space_free is the registered, 1-cycle-old view from sram_controller)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>m_axi_arvalid</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:413</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>m_axi_arvalid = w_arb_grant_valid &amp;&amp; sched_rd_valid[w_arb_grant_id]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = grant_valid/sched_rd_valid[gnt]   cols = </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
+          <t>space_free is registered twice on its way out of the SRAM controller; the read side tolerates the staleness because alloc reservations only shrink it (safe direction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>RTL (mirror of)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>w_transfer_size[i]</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>(sched_rd_beats &lt;= cfg+1) ? sched_rd_beats-1 : cfg</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>AxLEN value: full configured burst, or the shorter final burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>w_space_ok[i]</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>axi_rd_alloc_space_free[i] &gt;= w_transfer_size[i]+1</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>SRAM channel can hold the whole burst BEFORE the AR issues (pre-allocation; space_free is the registered, 1-cycle-old view from sram_controller)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>m_axi_arvalid</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:413</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>m_axi_arvalid = w_arb_grant_valid &amp;&amp; sched_rd_valid[w_arb_grant_id]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = grant_valid/sched_rd_valid[gnt]   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1). The sched_rd_valid term masks stale grants (r_arb_request pipeline). DESIGN NOTE: arvalid is combinational - if sched_rd_valid drops (error/reset/timeout escalation) while an AR waits for arready, arvalid retracts, which violates AXI valid-stability. Benign in the normal flow (valid only drops via the done-strobe look-ahead, i.e. after the handshake), but real on the abort paths.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="B41" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="B42" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B43" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="B44" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: grant_valid &amp; sched_rd_valid[gnt]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>w_arb_grant_ack[i]</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:429-431</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>ack[i] = (grant[i] &amp;&amp; m_axi_arvalid &amp;&amp; m_axi_arready) | (grant[i] &amp;&amp; !sched_rd_valid[i])   [for the granted channel, m_axi_arvalid == sched_rd_valid[i]]</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>rows = grant_i/sched_rd_valid_i   cols = arready</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY in the grant_i=1 half: at (1,1,1) the AR fired, at (1,0,x) the grant is STALE and auto-releases so the arbiter advances instead of waiting for an AR that can never fire. The (1,1,0) cell MUST be 0 - releasing a live grant before arready would re-arbitrate mid-handshake.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="B57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="B58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="10" t="n">
+      <c r="B59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B60" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C60" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: grant_i &amp; !sched_rd_valid_i  |  grant_i &amp; arready</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>r_outstanding_limit[i] next (PIPELINE=0)</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:193-210</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>set on (arvalid &amp;&amp; arready &amp;&amp; grant_id==i); clear on (rvalid &amp;&amp; rready &amp;&amp; rlast &amp;&amp; rid==i); independent ifs, clear written last so same-cycle AR+RLAST resolves to CLEAR (0)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = ar_fire_i/rlast_fire_i   cols = </t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: clear wins the (1,1) cell - the same-cycle AR/R fix (was else-if, which wedged the flag at 1). set only at (1,0).</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>hold</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>sched_rd_error[i] latch enable</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:520</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>latch r_rd_error[rid] on: m_axi_rvalid &amp;&amp; m_axi_rready &amp;&amp; (m_axi_rresp != 2'b00)   [resp_ok = (rresp==OKAY)]</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>rows = rvalid/rready   cols = resp_ok</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0): only an ACCEPTED bad beat latches the sticky error. A 1 with rready=0 would latch errors for beats that were never taken.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="8" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="B87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="B88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B68" s="10" t="n">
+      <c r="B89" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C68" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="C89" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="B90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: rvalid &amp; rready &amp; !resp_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
         <is>
           <t>R-channel accept / drain wiring (passthrough)</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_read_engine.sv:469-472</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>A beat accepted on R is by construction a beat written to the SRAM controller - the two counters (dbg_r_beats_rcvd / dbg_sram_writes) must always match.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>signal</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>RTL</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>axi_rd_sram_valid</t>
         </is>
       </c>
-      <c r="B75" s="4">
+      <c r="B98" s="4">
         <f> m_axi_rvalid</f>
         <v/>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>no buffering</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>axi_rd_sram_id</t>
         </is>
       </c>
-      <c r="B76" s="4">
+      <c r="B99" s="4">
         <f> m_axi_rid</f>
         <v/>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>channel routing</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>axi_rd_sram_data</t>
         </is>
       </c>
-      <c r="B77" s="4">
+      <c r="B100" s="4">
         <f> m_axi_rdata</f>
         <v/>
       </c>
-      <c r="C77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>m_axi_rready</t>
         </is>
       </c>
-      <c r="B78" s="4">
+      <c r="B101" s="4">
         <f> axi_rd_sram_ready</f>
         <v/>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>SRAM backpressure is the ONLY R backpressure</t>
         </is>
@@ -3430,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3490,737 +3759,933 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="B14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>w_data_ok[i]  (given sched_wr_valid[i])</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:427-434</t>
-        </is>
+      <c r="B15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: sched_wr_valid &amp; data_ok &amp; no_outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>w_data_ok[i]  (given sched_wr_valid[i])</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:427-434</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>w_data_ok = w_has_data || w_final_burst ; has_data = (w_effective_avail &gt;= transfer_size+1) ; final_burst = (0 &lt; sched_wr_beats &lt;= cfg+1) &amp;&amp; (w_effective_avail &gt;= sched_wr_beats)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = has_data/final_burst   cols = </t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: OR of the two comparator results: zero only at (0,0). final_burst lets the LAST, shorter burst of a descriptor go with exactly its remaining beats available.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B28" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B31" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: final_burst  |  has_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>w_effective_avail (stale-view race closure)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:384-411</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>axi_wr_drain_data_avail is registered twice on its way out of sram_controller (2-cycle-stale view). Without this subtraction the engine could fire an AW against beats an in-flight prior drain_req already claimed -&gt; over-drain -&gt; permanent occupancy corruption (see K-maps sram ctrl).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>RTL (mirror of)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>why</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>w_drain_t[ch]</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>awlen+1 on this cycle's AW handshake</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>drain_req size firing NOW</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>r_drain_tminus1[ch]</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>registered w_drain_t</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>drain_req that fired LAST cycle</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>w_pending_drain</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>r_drain_tminus1 + w_drain_t</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>in-flight drains not yet visible in the registered avail</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>w_effective_avail</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>avail &gt;= pending ? avail - pending : 0</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>the 'true' count drain_ctrl will reach when our drain lands</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>AW grant-capture enable</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:562</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>capture if (w_arb_grant_valid &amp;&amp; !r_aw_valid &amp;&amp; sched_wr_valid[w_arb_grant_id])</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>rows = grant_valid/r_aw_valid   cols = sched_wr_valid[gnt]</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,0,1): a new AW is captured only when no AW is pending and the grant is still live. The (1,0,0) cell MUST be 0 - that is the stale-grant guard (grant released via w_stale_grant instead).</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="B53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="B54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="B55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="10" t="n">
+      <c r="B56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>m_axi_wvalid</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:720-722</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>m_axi_wvalid = r_w_active &amp;&amp; axi_wr_sram_valid[ch] &amp;&amp; axi_wr_sram_valid_comb[ch]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>rows = r_w_active/valid_reg   cols = valid_comb</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). The (1,1,0) cell is the STALE-SKID window: registered valid still 1, but the muxed data wire shows stale skid contents - it MUST be 0 or stale data leaks onto AXI (the dma_2ch CRC-mismatch shape).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="9" t="n">
-        <v>0</v>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: grant_valid &amp; !r_aw_valid &amp; sched_wr_valid[gnt]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>axi_wr_sram_drain  (SRAM pop)</t>
+          <t>m_axi_wvalid</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:704</t>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:720-722</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>assign axi_wr_sram_drain = m_axi_wvalid &amp;&amp; m_axi_wready;</t>
+          <t>m_axi_wvalid = r_w_active &amp;&amp; axi_wr_sram_valid[ch] &amp;&amp; axi_wr_sram_valid_comb[ch]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = m_axi_wvalid/m_axi_wready   cols = </t>
+          <t>rows = r_w_active/valid_reg   cols = valid_comb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): pop exactly the beats actually transmitted. BUG FIX (lost-WLAST deadlock): the pre-fix 'r_w_active &amp;&amp; m_axi_wready' form put a 1 in the wvalid=0 column - the beat was consumed but never transmitted, and when it was the burst's final beat WLAST never rode a valid beat and the channel hung (found via the per-channel timing-skew 'mixed' profile, kept as regression sentinel). See projects/components/dmas/stream/known_issues/resolved/axi_write_engine_wlast_drain.md.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). The (1,1,0) cell is the STALE-SKID window: registered valid still 1, but the muxed data wire shows stale skid contents - it MUST be 0 or stale data leaks onto AXI (the dma_2ch CRC-mismatch shape).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="B69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="B70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B69" s="10" t="n">
+      <c r="B71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>w_phase_fifo_pop</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:776-787</t>
-        </is>
+      <c r="B72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: r_w_active &amp; valid_reg &amp; valid_comb</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_drain  (SRAM pop)</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:704</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>assign axi_wr_sram_drain = m_axi_wvalid &amp;&amp; m_axi_wready;</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = m_axi_wvalid/m_axi_wready   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): pop exactly the beats actually transmitted. BUG FIX (lost-WLAST deadlock): the pre-fix 'r_w_active &amp;&amp; m_axi_wready' form put a 1 in the wvalid=0 column - the beat was consumed but never transmitted, and when it was the burst's final beat WLAST never rode a valid beat and the channel hung (found via the per-channel timing-skew 'mixed' profile, kept as regression sentinel). See projects/components/dmas/stream/known_issues/resolved/axi_write_engine_wlast_drain.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: m_axi_wvalid &amp; m_axi_wready</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>w_phase_fifo_pop</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:776-787</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
           <t>pop = (!r_w_active &amp;&amp; !fifo_empty) || (m_axi_wvalid &amp;&amp; m_axi_wready &amp;&amp; m_axi_wlast &amp;&amp; !fifo_empty)   [w_fire = wvalid &amp;&amp; wready]</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>rows = r_w_active/fifo_empty   cols = w_fire/wlast</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s only in the fifo_empty=0 columns: start-from-idle (active=0) and burst-chain-through (w_fire &amp;&amp; wlast, no bubble between back-to-back bursts). Cells with active=0 &amp;&amp; w_fire=1 are unreachable (m_axi_wvalid requires r_w_active).</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="8" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B79" s="10" t="n">
+      <c r="B101" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C79" s="10" t="n">
+      <c r="C101" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D79" s="10" t="n">
+      <c r="D101" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="10" t="n">
+      <c r="E101" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="B102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="B103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="10" t="n">
+      <c r="B104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="E104" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !r_w_active &amp; !fifo_empty  |  !fifo_empty &amp; w_fire &amp; wlast</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
         <is>
           <t>sched_wr_error[i] latch enable</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:951</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>latch r_wr_error[bid] on: m_axi_bvalid &amp;&amp; m_axi_bready &amp;&amp; (m_axi_bresp != 2'b00)   [bready is constant 1]</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = bvalid/resp_ok   cols = </t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,0). bready==1 always (projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:941), so bvalid alone qualifies the beat.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="8" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B91" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="B117" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B92" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="B118" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B93" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="B119" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B94" s="10" t="n">
+      <c r="B120" s="11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: bvalid &amp; !resp_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4234,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4301,1795 +4766,2047 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="B15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>sched_wr_valid  (channel write kick)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1001-1005</t>
-        </is>
+      <c r="C16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: state_xfer &amp; !rd_done &amp; !completing_now &amp; !rd_need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>sched_wr_valid  (channel write kick)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1001-1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
           <t>sched_wr_valid = (state==CH_XFER_DATA) &amp;&amp; (r_write_beats_remaining != 0) &amp;&amp; !w_write_complete &amp;&amp; !w_sched_wr_completing_this_cycle &amp;&amp; !w_wr_need_base</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>rows = state_xfer/issue_rem_nz   cols = commit_zero/completing_now   pages = wr_need_base</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the wr_need_base=0 page, in the completing_now=0 columns, only at (state=1, rem=1, commit_zero=0). The explicit issue_rem_nz term is load-bearing: w_write_complete tracks COMMITS now, so without it the engine would keep valid high through the commit-wait with sched_wr_beats==0 and issue a garbage AW (transfer-size underflow -&gt; awlen=0xFF). NOTE commit_zero=1 with rem=1 cannot occur in practice (commits cannot complete before issue), so that half is unreachable cover, not a functional path.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>[wr_need_base=0]</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="B30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="B31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B32" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="C32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="B33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>[wr_need_base=1]</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="8" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="B37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="B38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="B39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="B40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: state_xfer &amp; issue_rem_nz &amp; !commit_zero &amp; !completing_now &amp; !wr_need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>w_addrgen_start  (run-base generator start; EXT only)</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:317</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>w_addrgen_start = w_state_fetch_desc &amp;&amp; !r_fetch_desc_d &amp;&amp; w_is_ext</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>rows = state_fetch_desc/entry_edge   cols = is_ext</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). The is_ext term is the TASK-059 FIX: without it a LEGACY descriptor also pulses start, running stream_run_addr_gen with its own base and STALE r_descriptor_ext strides. The generator's run-base FIFO has no flush (gaxi_fifo_sync clears only on rst_n) and legacy never consumes bases, so those bogus bases are consumed by the NEXT chained strided/transpose descriptor -&gt; reads the wrong source and writes into the previous descriptor's region (silent corruption). A contiguous EXT descriptor hides it (single-run generation emits zero bases). See known_issues/resolved/extended_chained_transpose.md.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="B53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="B54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="10" t="n">
+      <c r="B55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>w_transfer_complete  (per-descriptor advance gate)</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:906</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>w_transfer_complete = w_read_complete &amp;&amp; w_write_issued   [ISSUE-based on purpose: chained descriptors stream while their writes commit in the background]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = read_complete/write_issued   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1). Commit-gating this (as a past edit did) serializes the write drain at every descriptor boundary - the regression that motivated the issue/commit split.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>1</v>
+      <c r="B56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="n">
-        <v>0</v>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: state_fetch_desc &amp; entry_edge &amp; is_ext</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>CH_XFER_DATA exit decision</t>
+          <t>w_transfer_complete  (per-descriptor advance gate)</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:523-527</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:906</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>if (w_wr_advance) stay-XFER (in-place descriptor advance) ; else if (w_transfer_complete &amp;&amp; !r_rd_ahead) -&gt; CH_COMPLETE ; else hold</t>
+          <t>w_transfer_complete = w_read_complete &amp;&amp; w_write_issued   [ISSUE-based on purpose: chained descriptors stream while their writes commit in the background]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rows = wr_advance/transfer_complete   cols = rd_ahead</t>
+          <t xml:space="preserve">rows = read_complete/write_issued   cols = </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: advance fills the whole wr_advance=1 half (priority). COMPLETE only at (0,1,0): while read runs ahead (rd_ahead=1) the completion exit is SUPPRESSED because w_transfer_complete keys off the READ counter which already refers to descriptor N+1.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1). Commit-gating this (as a past edit did) serializes the write drain at every descriptor boundary - the regression that motivated the issue/commit split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="B69" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="B70" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="B71" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>CH_COMPLETE exit decision</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:540-544</t>
-        </is>
+      <c r="B72" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: read_complete &amp; write_issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>CH_XFER_DATA exit decision</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:523-527</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>if (w_wr_advance) stay-XFER (in-place descriptor advance) ; else if (w_transfer_complete &amp;&amp; !r_rd_ahead) -&gt; CH_COMPLETE ; else hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>rows = wr_advance/transfer_complete   cols = rd_ahead</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: advance fills the whole wr_advance=1 half (priority). COMPLETE only at (0,1,0): while read runs ahead (rd_ahead=1) the completion exit is SUPPRESSED because w_transfer_complete keys off the READ counter which already refers to descriptor N+1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>CH_COMPLETE exit decision</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:540-544</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
           <t>if (next_ptr != 0 &amp;&amp; !last) -&gt; CH_NEXT_DESC (advance NOW, issue-based) ; else if (w_write_complete) -&gt; CH_IDLE ; else hold</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = chained/write_complete   cols = </t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: chained=1 half advances immediately regardless of commits (streaming). IDLE only at (0,1): the LAST descriptor holds here until every write has COMMITTED - the channel is never reported done while data still drains.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="8" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>hold</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>IDLE</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>NEXT_DESC</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>NEXT_DESC</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>w_rd_peek  (read-ahead loads next descriptor)</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:929-931</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>w_rd_peek = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; !r_rd_ahead &amp;&amp; (r_read_beats_remaining==0) &amp;&amp; !w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid   [head_ok = w_desc_chained &amp;&amp; descriptor_valid]</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>rows = prefetch_en/state_xfer   cols = rd_ahead/rd_done   pages = write_issued/head_ok</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the [write_issued=0, head_ok=1] page, single cell (prefetch_en=1, state_xfer=1, rd_ahead=0, rd_done=1). rd_ahead=0 caps read-ahead at ONE descriptor; write_issued=0 means the write side still owns the FIFO head, so peek must NOT pop it.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>[write_issued=0, head_ok=0]</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="8" t="inlineStr">
+    <row r="113">
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="B114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="B115" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="B116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
+      <c r="B117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>[write_issued=0, head_ok=1]</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="8" t="inlineStr">
+    <row r="120">
+      <c r="B120" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E120" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="B121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="B122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" s="10" t="n">
+      <c r="B123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="D123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>[write_issued=1, head_ok=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>[write_issued=1, head_ok=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="inlineStr">
-        <is>
-          <t>w_wr_advance  (in-place descriptor advance + FIFO pop)</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:939-940</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>w_wr_advance = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>rows = prefetch_en/state_xfer   cols = write_issued/chained   pages = desc_valid</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the [desc_valid=1] page, single cell at all-ones. This is the ONLY XFER-state descriptor_ready source: it pops the FIFO head that peek borrowed. prefetch_en=0 forces the whole map to 0 (lockstep A/B on one bitstream).</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>[desc_valid=0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
+          <t>[write_issued=1, head_ok=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="9" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="9" t="n">
-        <v>0</v>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="B130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>[desc_valid=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
+          <t>[write_issued=1, head_ok=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="9" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="C134" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="9" t="n">
-        <v>0</v>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="B137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="inlineStr">
-        <is>
-          <t>descriptor_ready  (FIFO pop)</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1077-1079</t>
-        </is>
+      <c r="B138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>descriptor_ready = (state==CH_IDLE) || (state==CH_NEXT_DESC) || w_wr_advance</t>
+          <t>DERIVED MINIMAL SOP: prefetch_en &amp; state_xfer &amp; !rd_ahead &amp; rd_done &amp; !write_issued &amp; head_ok</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>rows = state_idle/state_next_desc   cols = wr_advance</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: OR of three sources; zero only at all-zeros. idle/next_desc are mutually exclusive (one-hot FSM) and wr_advance can only be 1 in CH_XFER_DATA, so at most one source is live per cycle - the (1,1,x) cells are unreachable cover.</t>
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>w_wr_advance  (in-place descriptor advance + FIFO pop)</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:939-940</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>w_wr_advance = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>rows = prefetch_en/state_xfer   cols = write_issued/chained   pages = desc_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s ONLY on the [desc_valid=1] page, single cell at all-ones. This is the ONLY XFER-state descriptor_ready source: it pops the FIFO head that peek borrowed. prefetch_en=0 forces the whole map to 0 (lockstep A/B on one bitstream).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>[desc_valid=0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="C151" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B146" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="D151" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B147" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="E151" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B148" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="inlineStr">
-        <is>
-          <t>w_hard_error  (fatal -&gt; sticky CH_ERROR)</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1170-1171</t>
-        </is>
-      </c>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky   [rd_any = live|sticky, wr_any = live|sticky]</t>
-        </is>
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>rows = descriptor_error/rd_any   cols = wr_any</t>
-        </is>
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at all-zeros (pure OR). A bare timeout window is deliberately NOT in this cone - it escalates separately via w_timeout_escalate (strikes &gt;= cfg_sched_timeout_limit).</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
+          <t>[desc_valid=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="9" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" s="10" t="n">
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="11" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
+      <c r="E161" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: prefetch_en &amp; state_xfer &amp; write_issued &amp; chained &amp; desc_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>descriptor_ready  (FIFO pop)</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1077-1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>descriptor_ready = (state==CH_IDLE) || (state==CH_NEXT_DESC) || w_wr_advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>rows = state_idle/state_next_desc   cols = wr_advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: OR of three sources; zero only at all-zeros. idle/next_desc are mutually exclusive (one-hot FSM) and wr_advance can only be 1 in CH_XFER_DATA, so at most one source is live per cycle - the (1,1,x) cells are unreachable cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B158" s="10" t="n">
+      <c r="B176" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C158" s="10" t="n">
+      <c r="C176" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="8" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B159" s="10" t="n">
+      <c r="B177" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C159" s="10" t="n">
+      <c r="C177" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="8" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B160" s="10" t="n">
+      <c r="B178" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C160" s="10" t="n">
+      <c r="C178" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: wr_advance  |  state_next_desc  |  state_idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>w_hard_error  (fatal -&gt; sticky CH_ERROR)</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1170-1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky   [rd_any = live|sticky, wr_any = live|sticky]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>rows = descriptor_error/rd_any   cols = wr_any</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at all-zeros (pure OR). A bare timeout window is deliberately NOT in this cone - it escalates separately via w_timeout_escalate (strikes &gt;= cfg_sched_timeout_limit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B193" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B194" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: wr_any  |  rd_any  |  descriptor_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
         <is>
           <t>r_timeout_counter next-value (priority order)</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1115-1123</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
         <is>
           <t>w_timeout_expired = cfg_sched_timeout_enable &amp;&amp; (counter &gt;= cfg_sched_timeout_cycles) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1147-1148). Escalation: w_timeout_escalate = (limit != 0) &amp;&amp; (strikes &gt;= limit) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1152-1153); strikes clear on any progress or CH_IDLE.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
         <is>
           <t>condition (first match wins)</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
         <is>
           <t>sched_wr_done_strobe || sched_wr_commit_strobe</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B202" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
+      <c r="C202" s="4" t="inlineStr">
         <is>
           <t>ANY write progress (AW issue OR B commit) re-arms - commits count as progress because completion is commit-gated</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t>w_timeout_expired</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C167" s="4" t="inlineStr">
+      <c r="C203" s="4" t="inlineStr">
         <is>
           <t>window elapsed -&gt; re-arm and keep waiting (SOFT timeout, one pulse per window)</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
         <is>
           <t>sched_wr_valid &amp;&amp; !sched_wr_ready</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="B204" s="4" t="inlineStr">
         <is>
           <t>counter + 1</t>
         </is>
       </c>
-      <c r="C168" s="4" t="inlineStr">
+      <c r="C204" s="4" t="inlineStr">
         <is>
           <t>genuinely waiting on the write engine</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
         <is>
           <t>otherwise</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="B205" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C205" s="4" t="inlineStr">
         <is>
           <t>not waiting</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
         <is>
           <t>FSM transition priority</t>
         </is>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D208" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:464-478</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="7" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
         <is>
           <t>CH_ERROR self-loops until channel reset; scheduler_idle reports CH_IDLE only (a wedged channel must NOT read idle).</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="4" t="n">
+    <row r="211">
+      <c r="A211" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B211" s="4" t="inlineStr">
         <is>
           <t>r_channel_reset_active</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C211" s="4" t="inlineStr">
         <is>
           <t>-&gt; CH_IDLE (overrides all)</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="4" t="n">
+    <row r="212">
+      <c r="A212" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B212" s="4" t="inlineStr">
         <is>
           <t>w_hard_error || w_timeout_escalate</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C212" s="4" t="inlineStr">
         <is>
           <t>-&gt; CH_ERROR (sticky)</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="4" t="n">
+    <row r="213">
+      <c r="A213" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B213" s="4" t="inlineStr">
         <is>
           <t>state case (normal transitions)</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C213" s="4" t="inlineStr">
         <is>
           <t>see exit-decision maps</t>
         </is>
@@ -6106,7 +6823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6166,954 +6883,1150 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="10" t="n">
+      <c r="B15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="11" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>w_chain_eligible  (level 2+3, throttle-independent)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:457-459</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: next_addr_nz &amp; !last &amp; valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>w_chain_eligible  (level 2+3, throttle-independent)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:457-459</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>w_chain_eligible = w_chain_condition &amp;&amp; w_next_addr_valid &amp;&amp; !r_descriptor_error   [next_addr_valid = in cfg_addr0 or cfg_addr1 window]</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>rows = chain_condition/addr_in_window   cols = descriptor_error</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,0). The window check is the runaway-chain guard: an out-of-window pointer silently ENDS the chain (engine idles; no error escalation).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="C30" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: chain_condition &amp; addr_in_window &amp; !descriptor_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>w_should_chain  (immediate chain push)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:479-480</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:496-480</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>w_should_chain = w_chain_eligible &amp;&amp; w_desc_committed &amp;&amp; w_prefetch_allows &amp;&amp; w_desc_addr_fifo_wr_ready   [committed = (state==RD_COMPLETE) &amp;&amp; desc-FIFO wr_ready]</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>rows = eligible/committed   cols = prefetch_allows/addr_fifo_ready</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at all-ones. eligible &amp;&amp; committed &amp;&amp; !push (throttled or FIFO full) does NOT lose the fetch - it arms r_chain_pending (deferred path below).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="B44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="B45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="10" t="n">
+      <c r="B46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="E46" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>w_pending_push_fire  (deferred chain push)</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:485-486</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>w_pending_push_fire = r_chain_pending &amp;&amp; w_prefetch_allows &amp;&amp; w_desc_addr_fifo_wr_ready &amp;&amp; !w_desc_committed</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>rows = chain_pending/prefetch_allows   cols = addr_fifo_ready/committed</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0). The !committed term keeps the commit cycle reserved for the immediate path - both pushing in one cycle would double-write the address FIFO mux.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>1</v>
+      <c r="B47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>0</v>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: eligible &amp; committed &amp; prefetch_allows &amp; addr_fifo_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
+          <t>w_pending_push_fire  (deferred chain push)</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:485-486</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>w_pending_push_fire = r_chain_pending &amp;&amp; w_prefetch_allows &amp;&amp; w_desc_addr_fifo_wr_ready &amp;&amp; !w_desc_committed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>rows = chain_pending/prefetch_allows   cols = addr_fifo_ready/committed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0). The !committed term keeps the commit cycle reserved for the immediate path - both pushing in one cycle would double-write the address FIFO mux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: chain_pending &amp; prefetch_allows &amp; addr_fifo_ready &amp; !committed</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
           <t>w_prefetch_limit  (chain throttle)</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:468-476</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>w_prefetch_allows = (w_desc_fifo_count &lt; w_prefetch_limit) (projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:476). BUG FIX: cfg_prefetch_enable / cfg_fifo_threshold were previously DEAD (unwired) - wiring them into this throttle was half of the top-level multi_channel/stress hang fix.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>cfg_prefetch_enable</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>cfg_fifo_threshold</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>on-demand: fetch next only after the scheduler drains the current descriptor</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>guard: threshold 0 would stall chaining forever</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>N&gt;0</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>buffer up to N fetched-but-unconsumed descriptors ahead of the scheduler</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>APB accept  (w_apb_skid_valid_in / apb_ready)</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:333-336</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>accept = apb_valid &amp;&amp; !r_channel_reset_active &amp;&amp; w_desc_addr_fifo_empty &amp;&amp; channel_idle &amp;&amp; !r_apb_ip   [apb_ready has the same gate off the skid ready]</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>rows = apb_valid/reset_active   cols = addr_fifo_empty/channel_idle   pages = apb_ip</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the apb_ip=0 page, in the channel_idle=1 columns, single cell (valid=1, reset=0, fifo_empty=1). fifo_empty prevents APB from clobbering a queued chain address; apb_ip prevents accepting a second kick before the first chain completes (cleared on the channel_idle falling edge).</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>[apb_ip=0]</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="8" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="B85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="B86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="B87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="10" t="n">
+      <c r="B88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="E88" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>[apb_ip=1]</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="8" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="B92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="B93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="B94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="B95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: apb_valid &amp; !reset_active &amp; addr_fifo_empty &amp; channel_idle &amp; !apb_ip</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>ar_valid  (descriptor fetch AR)</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:920-921</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>ar_valid = ((state==RD_ISSUE_ADDR) || (state==RD_ISSUE_ADDR2)) &amp;&amp; !r_axi_read_active</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>rows = st_issue_addr/st_issue_addr2   cols = read_active</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s only in the read_active=0 half. The (1,1,x) cells are unreachable (one-hot FSM). read_active latches on ar_ready and clears on the R response, so a state re-entry cannot double-issue the same AR.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="8" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="B108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B87" s="10" t="n">
+      <c r="B109" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C87" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="C109" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B88" s="10" t="n">
+      <c r="B110" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C88" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="C110" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B89" s="10" t="n">
+      <c r="B111" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C89" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="C111" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: st_issue_addr2 &amp; !read_active  |  st_issue_addr &amp; !read_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>descriptor_valid  (to scheduler)</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:1037</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>descriptor_valid = w_desc_fifo_rd_valid &amp;&amp; !r_descriptor_error</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = fifo_rd_valid/descriptor_error   cols = </t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,0): a latched fetch error blocks ALL buffered descriptors from reaching the scheduler until the error clears (RD_IDLE re-entry / channel reset).</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="8" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="B124" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="B125" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="B126" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B101" s="10" t="n">
+      <c r="B127" s="11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: fifo_rd_valid &amp; !descriptor_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7127,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7187,459 +8100,571 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B12" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B14" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>alloc release  (rd_ptr += 1, space freed)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:141</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>DERIVED MINIMAL SOP: alloc_req &amp; !wr_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>alloc release  (rd_ptr += 1, space freed)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:141</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>.rd_valid(axi_wr_sram_valid &amp;&amp; axi_wr_sram_ready)   [release fires on the BRIDGE-OUTPUT handshake, i.e. when a beat leaves the channel unit toward the write engine]</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = bridge_out_valid/bridge_out_ready   cols = </t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1). Space is freed at unit EXIT (not FIFO entry): a beat parked in the latency-bridge skid still occupies its reservation, so space_free can never over-report.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B28" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B29" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B31" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: bridge_out_valid &amp; bridge_out_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>space_free accounting chain (read side)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/stream_alloc_ctrl.sv:141, projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:310-316, projects/components/dmas/stream/rtl/fub/sram_controller.sv:257-267</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>The 2-flop stage is the 100 MHz timing closure for the 8-channel arbitration cone; false-pathing it was rejected because a stale grant handshake could latch the wrong channel.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>expression / register</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>staleness</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>alloc_ctrl</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>space_free = DEPTH - (wr_ptr - rd_ptr)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>combinational</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>sram_controller_unit</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>registered once</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>1 cycle</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>sram_controller wrapper</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>registered again (axi_rd_alloc_space_free port)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>2 cycles total</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>axi_read_engine</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>w_space_ok compares the stale view</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>safe: reservations only SHRINK the stale view</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>drain occupancy advance  (wr_ptr += 1)</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:184</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>.wr_valid(axi_rd_sram_valid &amp;&amp; axi_rd_sram_ready)   [data beat lands in the channel FIFO -&gt; data_available += 1]</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = rd_sram_valid/rd_sram_ready   cols = </t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1): occupancy counts only ACCEPTED beats.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="B53" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="B54" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B55" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>drain reserve advance  (rd_ptr += rd_size)</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:97-105</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>advance = rd_valid &amp;&amp; rd_ready &amp;&amp; !r_rd_empty   [rd_valid = axi_wr_drain_req (fires on AW handshake); rd_ready = !empty; advances by the FULL rd_size]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = drain_req/rd_empty   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0). DANGER cell: the advance is gated only on not-EMPTY, not on size&lt;=available - a reservation larger than the real occupancy makes rd_ptr overshoot wr_ptr and the wrap-corrected count reads ~DEPTH FOREVER (permanent corruption, all-channel freeze). A sim-only $error at projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:172-181 fires at the bad reservation; the write engine's w_effective_avail pipeline is the synthesis-side guarantee the reservation is never oversized.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="n">
+      <c r="B56" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="n">
-        <v>1</v>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: rd_sram_valid &amp; rd_sram_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
+          <t>drain reserve advance  (rd_ptr += rd_size)</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:97-105</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>advance = rd_valid &amp;&amp; rd_ready &amp;&amp; !r_rd_empty   [rd_valid = axi_wr_drain_req (fires on AW handshake); rd_ready = !empty; advances by the FULL rd_size]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = drain_req/rd_empty   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0). DANGER cell: the advance is gated only on not-EMPTY, not on size&lt;=available - a reservation larger than the real occupancy makes rd_ptr overshoot wr_ptr and the wrap-corrected count reads ~DEPTH FOREVER (permanent corruption, all-channel freeze). A sim-only $error at projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:172-181 fires at the bad reservation; the write engine's w_effective_avail pipeline is the synthesis-side guarantee the reservation is never oversized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: drain_req &amp; !rd_empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
           <t>axi_wr_drain_data_avail contract (write side)</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:282-307</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>BUG FIX (all-channel deadlock): the double-count let the write engine size a burst against beats that did not exist -&gt; over-drain -&gt; permanent occupancy corruption -&gt; stall at the head of the shared in-order W-phase FIFO froze all 8 channels (slow_producer profile). See projects/components/dmas/stream/known_issues/resolved/sram_drain_bridge_double_count.md. Excluding skid beats is conservative-safe: it can only delay an AW, never over-issue one.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>avail = drain_ctrl occupancy ONLY</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>assign axi_wr_drain_data_avail = drain_data_available; (w_count of the drain virtual FIFO)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>bridge_occupancy is EXCLUDED</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>a beat in the latency-bridge skid is still counted by drain_ctrl (its rd_ptr only moves on drain_req), so adding bridge_occupancy counted it TWICE</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>registered once more at the wrapper</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/sram_controller.sv:257-267 -&gt; the write engine sees a 2-cycle-stale view and compensates with w_effective_avail</t>
         </is>
